--- a/artfynd/A 63185-2025 artfynd.xlsx
+++ b/artfynd/A 63185-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1854,45 +1854,59 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133012330</v>
+        <v>136679647</v>
       </c>
       <c r="B11" t="n">
-        <v>108205</v>
+        <v>58167</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220083</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bofalla, Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477484</v>
+        <v>477437</v>
       </c>
       <c r="R11" t="n">
-        <v>6595329</v>
+        <v>6595415</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1919,22 +1933,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1960,58 +1979,73 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133012330</t>
+          <t>https://artportalen.se/Sighting/136679647</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132914412</v>
+        <v>136679796</v>
       </c>
       <c r="B12" t="n">
-        <v>98060</v>
+        <v>58167</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rockesholm, Vrm</t>
+          <t>Bofalla, Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477397</v>
+        <v>477495</v>
       </c>
       <c r="R12" t="n">
-        <v>6595536</v>
+        <v>6595350</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2035,17 +2069,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2060,16 +2099,239 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136679796</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133012330</v>
+      </c>
+      <c r="B13" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bofalla, Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>477484</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6595329</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133012330</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132914412</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>477397</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6595536</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132914412</t>
         </is>
@@ -2088,6 +2350,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63185-2025 artfynd.xlsx
+++ b/artfynd/A 63185-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125740088</v>
+        <v>136710326</v>
       </c>
       <c r="B2" t="n">
-        <v>58114</v>
+        <v>57927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,44 +691,50 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bofalla, Bofalla, Vrm</t>
+          <t>Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477491</v>
+        <v>477624</v>
       </c>
       <c r="R2" t="n">
-        <v>6595212</v>
+        <v>6595314</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,22 +761,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>04:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>04:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,16 +802,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125740088</t>
+          <t>https://artportalen.se/Sighting/136710326</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126556846</v>
+        <v>136710614</v>
       </c>
       <c r="B3" t="n">
-        <v>58114</v>
+        <v>58019</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,41 +819,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -860,7 +854,7 @@
         <v>477564</v>
       </c>
       <c r="R3" t="n">
-        <v>6595455</v>
+        <v>6595312</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,22 +881,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,65 +922,67 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126556846</t>
+          <t>https://artportalen.se/Sighting/136710614</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131150481</v>
+        <v>136710940</v>
       </c>
       <c r="B4" t="n">
-        <v>58114</v>
+        <v>58003</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>permanent revir</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bofalla, Bofalla, Vrm</t>
+          <t>Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477517</v>
+        <v>477599</v>
       </c>
       <c r="R4" t="n">
-        <v>6595311</v>
+        <v>6595324</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,22 +1009,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,38 +1055,38 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131150481</t>
+          <t>https://artportalen.se/Sighting/136710940</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133011044</v>
+        <v>136710989</v>
       </c>
       <c r="B5" t="n">
-        <v>58136</v>
+        <v>58003</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1093,15 +1094,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1111,10 +1108,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477557</v>
+        <v>477572</v>
       </c>
       <c r="R5" t="n">
-        <v>6595249</v>
+        <v>6595289</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1141,27 +1138,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spel/sång.</t>
+          <t>Spel/sång</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1187,54 +1184,46 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133011044</t>
+          <t>https://artportalen.se/Sighting/136710989</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133015499</v>
+        <v>136711032</v>
       </c>
       <c r="B6" t="n">
-        <v>58136</v>
+        <v>58003</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1244,10 +1233,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477638</v>
+        <v>477547</v>
       </c>
       <c r="R6" t="n">
-        <v>6595421</v>
+        <v>6595295</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,27 +1263,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spel/sång.</t>
+          <t>Spel/sång</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1320,50 +1309,42 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133015499</t>
+          <t>https://artportalen.se/Sighting/136711032</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133039996</v>
+        <v>136711079</v>
       </c>
       <c r="B7" t="n">
-        <v>58136</v>
+        <v>58003</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
@@ -1373,14 +1354,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bofalla, Bofalla, Vrm</t>
+          <t>Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477688</v>
+        <v>477567</v>
       </c>
       <c r="R7" t="n">
-        <v>6595315</v>
+        <v>6595293</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1407,27 +1388,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Spel/sång i lämplig häckningsmiljö.</t>
+          <t>Spel/sång</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1453,50 +1434,42 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133039996</t>
+          <t>https://artportalen.se/Sighting/136711079</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133040185</v>
+        <v>136711102</v>
       </c>
       <c r="B8" t="n">
-        <v>58136</v>
+        <v>58003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
@@ -1506,14 +1479,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bofalla, Bofalla, Vrm</t>
+          <t>Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477544</v>
+        <v>477690</v>
       </c>
       <c r="R8" t="n">
-        <v>6595368</v>
+        <v>6595310</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1540,27 +1513,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Spel/sång i lämplig häckningsmiljö.</t>
+          <t>Spel/sång</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1586,38 +1559,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133040185</t>
+          <t>https://artportalen.se/Sighting/136711102</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134226087</v>
+        <v>136710589</v>
       </c>
       <c r="B9" t="n">
-        <v>58136</v>
+        <v>57184</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1630,21 +1603,23 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>permanent revir</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bofalla, Bofalla, Vrm</t>
+          <t>Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477605</v>
+        <v>477593</v>
       </c>
       <c r="R9" t="n">
-        <v>6595369</v>
+        <v>6595305</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1671,27 +1646,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Spel/sång.</t>
+          <t>Spel/sång</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1717,16 +1692,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134226087</t>
+          <t>https://artportalen.se/Sighting/136710589</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134226565</v>
+        <v>136710395</v>
       </c>
       <c r="B10" t="n">
-        <v>58136</v>
+        <v>58550</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,21 +1709,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>102990</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1761,21 +1736,23 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bofalla, Bofalla, Vrm</t>
+          <t>Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477555</v>
+        <v>477605</v>
       </c>
       <c r="R10" t="n">
-        <v>6595400</v>
+        <v>6595349</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1802,27 +1779,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Spel/sång.</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1848,16 +1820,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134226565</t>
+          <t>https://artportalen.se/Sighting/136710395</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136679647</v>
+        <v>136710403</v>
       </c>
       <c r="B11" t="n">
-        <v>58167</v>
+        <v>58550</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,48 +1837,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>102990</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bofalla, Bofalla, Vrm</t>
+          <t>Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477437</v>
+        <v>477577</v>
       </c>
       <c r="R11" t="n">
-        <v>6595415</v>
+        <v>6595325</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1933,27 +1899,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spel/sång.</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1979,16 +1940,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136679647</t>
+          <t>https://artportalen.se/Sighting/136710403</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136679796</v>
+        <v>136710413</v>
       </c>
       <c r="B12" t="n">
-        <v>58167</v>
+        <v>58550</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1996,53 +1957,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>102990</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bofalla, Bofalla, Vrm</t>
+          <t>Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477495</v>
+        <v>477656</v>
       </c>
       <c r="R12" t="n">
-        <v>6595350</v>
+        <v>6595324</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2069,22 +2019,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2110,51 +2050,59 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136679796</t>
+          <t>https://artportalen.se/Sighting/136710413</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133012330</v>
+        <v>136710423</v>
       </c>
       <c r="B13" t="n">
-        <v>108205</v>
+        <v>58550</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220083</v>
+        <v>102990</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bofalla, Bofalla, Vrm</t>
+          <t>Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477484</v>
+        <v>477645</v>
       </c>
       <c r="R13" t="n">
-        <v>6595329</v>
+        <v>6595296</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2181,22 +2129,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2222,58 +2170,62 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133012330</t>
+          <t>https://artportalen.se/Sighting/136710423</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132914412</v>
+        <v>136710510</v>
       </c>
       <c r="B14" t="n">
-        <v>98060</v>
+        <v>58550</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>102990</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rockesholm, Vrm</t>
+          <t>Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477397</v>
+        <v>477615</v>
       </c>
       <c r="R14" t="n">
-        <v>6595536</v>
+        <v>6595293</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2297,17 +2249,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2322,16 +2279,1915 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136710510</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136710526</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58550</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>477650</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6595318</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136710526</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136710555</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58550</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>477626</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6595328</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136710555</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125740088</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bofalla, Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>477491</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6595212</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125740088</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126556846</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>477564</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6595455</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126556846</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131150481</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bofalla, Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>477517</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6595311</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131150481</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133011044</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>477557</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6595249</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133011044</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>133015499</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>477638</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6595421</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133015499</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>133039996</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bofalla, Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>477688</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6595315</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spel/sång i lämplig häckningsmiljö.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133039996</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>133040185</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bofalla, Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>477544</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6595368</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>05:51</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>05:51</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Spel/sång i lämplig häckningsmiljö.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133040185</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134226087</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bofalla, Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>477605</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6595369</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134226087</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134226565</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bofalla, Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>477555</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6595400</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134226565</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136679647</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bofalla, Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>477437</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6595415</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136679647</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136679796</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bofalla, Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>477495</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6595350</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136679796</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>133012330</v>
+      </c>
+      <c r="B28" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bofalla, Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>477484</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6595329</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133012330</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132914412</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vrm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>477397</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6595536</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132914412</t>
         </is>
@@ -2352,6 +4208,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63185-2025 artfynd.xlsx
+++ b/artfynd/A 63185-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ29"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1565,10 +1565,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136710589</v>
+        <v>136721700</v>
       </c>
       <c r="B9" t="n">
-        <v>57184</v>
+        <v>58003</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1576,16 +1576,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1593,16 +1593,8 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
@@ -1616,10 +1608,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477593</v>
+        <v>477442</v>
       </c>
       <c r="R9" t="n">
-        <v>6595305</v>
+        <v>6595415</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1646,22 +1638,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1692,33 +1684,33 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136710589</t>
+          <t>https://artportalen.se/Sighting/136721700</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136710395</v>
+        <v>136710589</v>
       </c>
       <c r="B10" t="n">
-        <v>58550</v>
+        <v>57184</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102990</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1739,7 +1731,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1749,10 +1741,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477605</v>
+        <v>477593</v>
       </c>
       <c r="R10" t="n">
-        <v>6595349</v>
+        <v>6595305</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1779,22 +1771,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1820,13 +1817,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136710395</t>
+          <t>https://artportalen.se/Sighting/136710589</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136710403</v>
+        <v>136710395</v>
       </c>
       <c r="B11" t="n">
         <v>58550</v>
@@ -1854,8 +1851,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
@@ -1869,10 +1874,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477577</v>
+        <v>477605</v>
       </c>
       <c r="R11" t="n">
-        <v>6595325</v>
+        <v>6595349</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1899,22 +1904,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1940,13 +1945,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136710403</t>
+          <t>https://artportalen.se/Sighting/136710395</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136710413</v>
+        <v>136710403</v>
       </c>
       <c r="B12" t="n">
         <v>58550</v>
@@ -1989,10 +1994,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477656</v>
+        <v>477577</v>
       </c>
       <c r="R12" t="n">
-        <v>6595324</v>
+        <v>6595325</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2019,12 +2024,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>07:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>07:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2050,13 +2065,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136710413</t>
+          <t>https://artportalen.se/Sighting/136710403</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136710423</v>
+        <v>136710413</v>
       </c>
       <c r="B13" t="n">
         <v>58550</v>
@@ -2099,10 +2114,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477645</v>
+        <v>477656</v>
       </c>
       <c r="R13" t="n">
-        <v>6595296</v>
+        <v>6595324</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2132,19 +2147,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2170,13 +2175,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136710423</t>
+          <t>https://artportalen.se/Sighting/136710413</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136710510</v>
+        <v>136710423</v>
       </c>
       <c r="B14" t="n">
         <v>58550</v>
@@ -2219,10 +2224,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477615</v>
+        <v>477645</v>
       </c>
       <c r="R14" t="n">
-        <v>6595293</v>
+        <v>6595296</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2254,7 +2259,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2264,7 +2269,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2290,13 +2295,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136710510</t>
+          <t>https://artportalen.se/Sighting/136710423</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136710526</v>
+        <v>136710510</v>
       </c>
       <c r="B15" t="n">
         <v>58550</v>
@@ -2339,10 +2344,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477650</v>
+        <v>477615</v>
       </c>
       <c r="R15" t="n">
-        <v>6595318</v>
+        <v>6595293</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2369,22 +2374,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2410,13 +2415,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136710526</t>
+          <t>https://artportalen.se/Sighting/136710510</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136710555</v>
+        <v>136710526</v>
       </c>
       <c r="B16" t="n">
         <v>58550</v>
@@ -2459,10 +2464,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477626</v>
+        <v>477650</v>
       </c>
       <c r="R16" t="n">
-        <v>6595328</v>
+        <v>6595318</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2489,22 +2494,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2530,16 +2535,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136710555</t>
+          <t>https://artportalen.se/Sighting/136710526</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125740088</v>
+        <v>136710555</v>
       </c>
       <c r="B17" t="n">
-        <v>58114</v>
+        <v>58550</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2547,44 +2552,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>102990</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bofalla, Bofalla, Vrm</t>
+          <t>Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477491</v>
+        <v>477626</v>
       </c>
       <c r="R17" t="n">
-        <v>6595212</v>
+        <v>6595328</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2611,22 +2614,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2652,16 +2655,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125740088</t>
+          <t>https://artportalen.se/Sighting/136710555</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126556846</v>
+        <v>136721693</v>
       </c>
       <c r="B18" t="n">
-        <v>58114</v>
+        <v>58550</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2669,38 +2672,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>102990</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -2713,10 +2708,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477564</v>
+        <v>477410</v>
       </c>
       <c r="R18" t="n">
-        <v>6595455</v>
+        <v>6595459</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2743,22 +2738,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2784,13 +2784,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126556846</t>
+          <t>https://artportalen.se/Sighting/136721693</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131150481</v>
+        <v>125740088</v>
       </c>
       <c r="B19" t="n">
         <v>58114</v>
@@ -2818,14 +2818,10 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>i par</t>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2839,10 +2835,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477517</v>
+        <v>477491</v>
       </c>
       <c r="R19" t="n">
-        <v>6595311</v>
+        <v>6595212</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2869,22 +2865,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2910,16 +2906,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131150481</t>
+          <t>https://artportalen.se/Sighting/125740088</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133011044</v>
+        <v>126556846</v>
       </c>
       <c r="B20" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2946,7 +2942,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2954,10 +2950,14 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477557</v>
+        <v>477564</v>
       </c>
       <c r="R20" t="n">
-        <v>6595249</v>
+        <v>6595455</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2997,27 +2997,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Spel/sång.</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3043,16 +3038,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133011044</t>
+          <t>https://artportalen.se/Sighting/126556846</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133015499</v>
+        <v>131150481</v>
       </c>
       <c r="B21" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3079,31 +3074,29 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bofalla, Vrm</t>
+          <t>Bofalla, Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477638</v>
+        <v>477517</v>
       </c>
       <c r="R21" t="n">
-        <v>6595421</v>
+        <v>6595311</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3130,27 +3123,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Spel/sång.</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3176,13 +3164,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133015499</t>
+          <t>https://artportalen.se/Sighting/131150481</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133039996</v>
+        <v>133011044</v>
       </c>
       <c r="B22" t="n">
         <v>58136</v>
@@ -3223,20 +3211,20 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bofalla, Bofalla, Vrm</t>
+          <t>Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477688</v>
+        <v>477557</v>
       </c>
       <c r="R22" t="n">
-        <v>6595315</v>
+        <v>6595249</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3263,27 +3251,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Spel/sång i lämplig häckningsmiljö.</t>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3309,13 +3297,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133039996</t>
+          <t>https://artportalen.se/Sighting/133011044</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133040185</v>
+        <v>133015499</v>
       </c>
       <c r="B23" t="n">
         <v>58136</v>
@@ -3356,20 +3344,20 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bofalla, Bofalla, Vrm</t>
+          <t>Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477544</v>
+        <v>477638</v>
       </c>
       <c r="R23" t="n">
-        <v>6595368</v>
+        <v>6595421</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3396,27 +3384,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Spel/sång i lämplig häckningsmiljö.</t>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3442,13 +3430,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133040185</t>
+          <t>https://artportalen.se/Sighting/133015499</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134226087</v>
+        <v>133039996</v>
       </c>
       <c r="B24" t="n">
         <v>58136</v>
@@ -3486,21 +3474,23 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>permanent revir</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bofalla, Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477605</v>
+        <v>477688</v>
       </c>
       <c r="R24" t="n">
-        <v>6595369</v>
+        <v>6595315</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3527,27 +3517,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Spel/sång.</t>
+          <t>Spel/sång i lämplig häckningsmiljö.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3573,13 +3563,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134226087</t>
+          <t>https://artportalen.se/Sighting/133039996</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134226565</v>
+        <v>133040185</v>
       </c>
       <c r="B25" t="n">
         <v>58136</v>
@@ -3617,21 +3607,23 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>permanent revir</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bofalla, Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477555</v>
+        <v>477544</v>
       </c>
       <c r="R25" t="n">
-        <v>6595400</v>
+        <v>6595368</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3658,27 +3650,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Spel/sång.</t>
+          <t>Spel/sång i lämplig häckningsmiljö.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3704,16 +3696,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134226565</t>
+          <t>https://artportalen.se/Sighting/133040185</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136679647</v>
+        <v>134226087</v>
       </c>
       <c r="B26" t="n">
-        <v>58167</v>
+        <v>58136</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,10 +3751,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477437</v>
+        <v>477605</v>
       </c>
       <c r="R26" t="n">
-        <v>6595415</v>
+        <v>6595369</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3789,22 +3781,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3835,16 +3827,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136679647</t>
+          <t>https://artportalen.se/Sighting/134226087</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136679796</v>
+        <v>134226565</v>
       </c>
       <c r="B27" t="n">
-        <v>58167</v>
+        <v>58136</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3871,7 +3863,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3879,11 +3871,6 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -3895,10 +3882,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477495</v>
+        <v>477555</v>
       </c>
       <c r="R27" t="n">
-        <v>6595350</v>
+        <v>6595400</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3925,22 +3912,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3966,51 +3958,65 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136679796</t>
+          <t>https://artportalen.se/Sighting/134226565</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133012330</v>
+        <v>136679647</v>
       </c>
       <c r="B28" t="n">
-        <v>108205</v>
+        <v>58167</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220083</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bofalla, Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477484</v>
+        <v>477437</v>
       </c>
       <c r="R28" t="n">
-        <v>6595329</v>
+        <v>6595415</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4037,22 +4043,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4078,58 +4089,73 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133012330</t>
+          <t>https://artportalen.se/Sighting/136679647</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132914412</v>
+        <v>136679796</v>
       </c>
       <c r="B29" t="n">
-        <v>98060</v>
+        <v>58167</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rockesholm, Vrm</t>
+          <t>Bofalla, Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477397</v>
+        <v>477495</v>
       </c>
       <c r="R29" t="n">
-        <v>6595536</v>
+        <v>6595350</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4153,17 +4179,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4178,16 +4209,3503 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136679796</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136721202</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>477587</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6595316</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>06:46</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>06:46</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721202</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136721217</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>477669</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6595301</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721217</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136721223</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>477676</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6595323</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721223</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136721231</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>477614</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6595311</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721231</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136721238</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>477561</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6595333</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721238</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136721263</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>477579</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6595304</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721263</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136721280</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>477585</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6595345</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721280</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136721286</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>477580</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6595309</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>06:06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>06:06</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721286</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136721297</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>477596</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6595294</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721297</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>136721322</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>477556</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6595306</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721322</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136721334</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>477640</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6595307</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721334</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136721357</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>477646</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6595333</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721357</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>136721370</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>477628</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6595299</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>06:19</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>06:19</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721370</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>136721387</v>
+      </c>
+      <c r="B43" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>477617</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6595312</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721387</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136721424</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>477615</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6595327</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721424</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>136721440</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>477599</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6595310</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721440</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>136721450</v>
+      </c>
+      <c r="B46" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>477642</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6595312</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721450</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>136721458</v>
+      </c>
+      <c r="B47" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>477633</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6595288</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721458</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>136721467</v>
+      </c>
+      <c r="B48" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>477594</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6595314</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721467</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>136721800</v>
+      </c>
+      <c r="B49" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>477419</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6595439</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721800</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>136721814</v>
+      </c>
+      <c r="B50" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>477431</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6595419</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721814</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>136721822</v>
+      </c>
+      <c r="B51" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>477433</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6595431</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>06:55</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>06:55</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721822</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>136721847</v>
+      </c>
+      <c r="B52" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>477435</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6595433</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721847</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>136721853</v>
+      </c>
+      <c r="B53" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>477431</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6595408</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721853</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>136721858</v>
+      </c>
+      <c r="B54" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>477433</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6595446</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721858</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>136721902</v>
+      </c>
+      <c r="B55" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>477439</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6595431</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136721902</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>133012330</v>
+      </c>
+      <c r="B56" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Bofalla, Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>477484</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6595329</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133012330</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>132914412</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vrm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>477397</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6595536</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132914412</t>
         </is>
@@ -4223,6 +7741,34 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63185-2025 artfynd.xlsx
+++ b/artfynd/A 63185-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ57"/>
+  <dimension ref="A1:AZ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136710326</v>
       </c>
       <c r="B2" t="n">
-        <v>57927</v>
+        <v>57929</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>136710614</v>
       </c>
       <c r="B3" t="n">
-        <v>58019</v>
+        <v>58021</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>136710940</v>
       </c>
       <c r="B4" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>136710989</v>
       </c>
       <c r="B5" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136711032</v>
       </c>
       <c r="B6" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>136711079</v>
       </c>
       <c r="B7" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>136711102</v>
       </c>
       <c r="B8" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136721700</v>
       </c>
       <c r="B9" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136710589</v>
       </c>
       <c r="B10" t="n">
-        <v>57184</v>
+        <v>57186</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>136710395</v>
       </c>
       <c r="B11" t="n">
-        <v>58550</v>
+        <v>58552</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>136710403</v>
       </c>
       <c r="B12" t="n">
-        <v>58550</v>
+        <v>58552</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>136710413</v>
       </c>
       <c r="B13" t="n">
-        <v>58550</v>
+        <v>58552</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>136710423</v>
       </c>
       <c r="B14" t="n">
-        <v>58550</v>
+        <v>58552</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>136710510</v>
       </c>
       <c r="B15" t="n">
-        <v>58550</v>
+        <v>58552</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136710526</v>
       </c>
       <c r="B16" t="n">
-        <v>58550</v>
+        <v>58552</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>136710555</v>
       </c>
       <c r="B17" t="n">
-        <v>58550</v>
+        <v>58552</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>136721693</v>
       </c>
       <c r="B18" t="n">
-        <v>58550</v>
+        <v>58552</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>136679647</v>
       </c>
       <c r="B28" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>136679796</v>
       </c>
       <c r="B29" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>136721202</v>
       </c>
       <c r="B30" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>136721217</v>
       </c>
       <c r="B31" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>136721223</v>
       </c>
       <c r="B32" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>136721231</v>
       </c>
       <c r="B33" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136721238</v>
       </c>
       <c r="B34" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>136721263</v>
       </c>
       <c r="B35" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>136721280</v>
       </c>
       <c r="B36" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>136721286</v>
       </c>
       <c r="B37" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>136721297</v>
       </c>
       <c r="B38" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>136721322</v>
       </c>
       <c r="B39" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>136721334</v>
       </c>
       <c r="B40" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>136721357</v>
       </c>
       <c r="B41" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>136721370</v>
       </c>
       <c r="B42" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>136721387</v>
       </c>
       <c r="B43" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>136721424</v>
       </c>
       <c r="B44" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>136721440</v>
       </c>
       <c r="B45" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>136721450</v>
       </c>
       <c r="B46" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>136721458</v>
       </c>
       <c r="B47" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>136721467</v>
       </c>
       <c r="B48" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>136721800</v>
       </c>
       <c r="B49" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>136721814</v>
       </c>
       <c r="B50" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>136721822</v>
       </c>
       <c r="B51" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>136721847</v>
       </c>
       <c r="B52" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>136721853</v>
       </c>
       <c r="B53" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>136721858</v>
       </c>
       <c r="B54" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>136721902</v>
       </c>
       <c r="B55" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7490,45 +7490,59 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133012330</v>
+        <v>136782770</v>
       </c>
       <c r="B56" t="n">
-        <v>108205</v>
+        <v>58169</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220083</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bofalla, Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>477484</v>
+        <v>477552</v>
       </c>
       <c r="R56" t="n">
-        <v>6595329</v>
+        <v>6595367</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7555,22 +7569,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7596,38 +7610,38 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133012330</t>
+          <t>https://artportalen.se/Sighting/136782770</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132914412</v>
+        <v>136782909</v>
       </c>
       <c r="B57" t="n">
-        <v>98060</v>
+        <v>58169</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -7635,19 +7649,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Rockesholm, Vrm</t>
+          <t>Bofalla, Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>477397</v>
+        <v>477482</v>
       </c>
       <c r="R57" t="n">
-        <v>6595536</v>
+        <v>6595292</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7671,17 +7695,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7696,16 +7730,239 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136782909</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>133012330</v>
+      </c>
+      <c r="B58" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Bofalla, Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>477484</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6595329</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133012330</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>132914412</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vrm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>477397</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6595536</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132914412</t>
         </is>
@@ -7769,6 +8026,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63185-2025 artfynd.xlsx
+++ b/artfynd/A 63185-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ59"/>
+  <dimension ref="A1:AZ71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7747,10 +7747,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133012330</v>
+        <v>136950604</v>
       </c>
       <c r="B58" t="n">
-        <v>108205</v>
+        <v>56873</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7758,34 +7758,51 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220083</v>
+        <v>205988</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Tajgafladdermus</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Myotis brandtii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Eversmann, 1845)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bofalla, Bofalla, Vrm</t>
+          <t>Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>477484</v>
+        <v>477549</v>
       </c>
       <c r="R58" t="n">
-        <v>6595329</v>
+        <v>6595394</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7812,22 +7829,27 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>22:08</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ekolokalisation</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7853,16 +7875,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133012330</t>
+          <t>https://artportalen.se/Sighting/136950604</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132914412</v>
+        <v>136950780</v>
       </c>
       <c r="B59" t="n">
-        <v>98060</v>
+        <v>56875</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7870,21 +7892,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>205992</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -7892,19 +7914,32 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Rockesholm, Vrm</t>
+          <t>Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>477397</v>
+        <v>477490</v>
       </c>
       <c r="R59" t="n">
-        <v>6595536</v>
+        <v>6595271</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7928,17 +7963,27 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Ekolokalisation.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7953,16 +7998,1551 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136950780</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>136950792</v>
+      </c>
+      <c r="B60" t="n">
+        <v>56875</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>477498</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6595282</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>01:10</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>01:10</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ekolokalisation.</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136950792</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>136950831</v>
+      </c>
+      <c r="B61" t="n">
+        <v>56866</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>477494</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6595350</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ekolokalisation.</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136950831</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>136950991</v>
+      </c>
+      <c r="B62" t="n">
+        <v>56866</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>477498</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6595370</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ekolokalisation.</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136950991</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>136951403</v>
+      </c>
+      <c r="B63" t="n">
+        <v>56866</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>477494</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6595331</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>23:29</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>23:29</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ekolokalisation.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136951403</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>136951408</v>
+      </c>
+      <c r="B64" t="n">
+        <v>56866</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>477477</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6595300</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>01:31</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>01:31</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ekolokalisation.</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136951408</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>136951430</v>
+      </c>
+      <c r="B65" t="n">
+        <v>56866</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>477467</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6595271</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>20:19</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>20:19</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ekolokalisation,</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136951430</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>136951433</v>
+      </c>
+      <c r="B66" t="n">
+        <v>56866</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>477479</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6595373</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>21:03</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>21:03</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ekolokalisation.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136951433</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>136951435</v>
+      </c>
+      <c r="B67" t="n">
+        <v>56866</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>477496</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6595311</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>21:33</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>21:33</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ekolokalisation.</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136951435</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>136951986</v>
+      </c>
+      <c r="B68" t="n">
+        <v>56892</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>206000</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Gråskimlig fladdermus</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Vespertilio murinus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>477484</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6595323</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>20:19</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>20:19</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Socialt läte.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136951986</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>136950615</v>
+      </c>
+      <c r="B69" t="n">
+        <v>56889</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>477535</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6595416</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>22:07</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>22:07</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ekolokalisation.</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136950615</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>133012330</v>
+      </c>
+      <c r="B70" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Bofalla, Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>477484</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6595329</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133012330</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>132914412</v>
+      </c>
+      <c r="B71" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vrm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>477397</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6595536</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132914412</t>
         </is>
@@ -8028,6 +9608,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63185-2025 artfynd.xlsx
+++ b/artfynd/A 63185-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136710326</v>
       </c>
       <c r="B2" t="n">
-        <v>57929</v>
+        <v>57942</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>136710614</v>
       </c>
       <c r="B3" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>136710940</v>
       </c>
       <c r="B4" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>136710989</v>
       </c>
       <c r="B5" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136711032</v>
       </c>
       <c r="B6" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>136711079</v>
       </c>
       <c r="B7" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>136711102</v>
       </c>
       <c r="B8" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136721700</v>
       </c>
       <c r="B9" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136710589</v>
       </c>
       <c r="B10" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>136710395</v>
       </c>
       <c r="B11" t="n">
-        <v>58552</v>
+        <v>58565</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>136710403</v>
       </c>
       <c r="B12" t="n">
-        <v>58552</v>
+        <v>58565</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>136710413</v>
       </c>
       <c r="B13" t="n">
-        <v>58552</v>
+        <v>58565</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>136710423</v>
       </c>
       <c r="B14" t="n">
-        <v>58552</v>
+        <v>58565</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>136710510</v>
       </c>
       <c r="B15" t="n">
-        <v>58552</v>
+        <v>58565</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136710526</v>
       </c>
       <c r="B16" t="n">
-        <v>58552</v>
+        <v>58565</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>136710555</v>
       </c>
       <c r="B17" t="n">
-        <v>58552</v>
+        <v>58565</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>136721693</v>
       </c>
       <c r="B18" t="n">
-        <v>58552</v>
+        <v>58565</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>136679647</v>
       </c>
       <c r="B28" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>136679796</v>
       </c>
       <c r="B29" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>136721202</v>
       </c>
       <c r="B30" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>136721217</v>
       </c>
       <c r="B31" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>136721223</v>
       </c>
       <c r="B32" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>136721231</v>
       </c>
       <c r="B33" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136721238</v>
       </c>
       <c r="B34" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>136721263</v>
       </c>
       <c r="B35" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>136721280</v>
       </c>
       <c r="B36" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>136721286</v>
       </c>
       <c r="B37" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>136721297</v>
       </c>
       <c r="B38" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>136721322</v>
       </c>
       <c r="B39" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>136721334</v>
       </c>
       <c r="B40" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>136721357</v>
       </c>
       <c r="B41" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>136721370</v>
       </c>
       <c r="B42" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>136721387</v>
       </c>
       <c r="B43" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>136721424</v>
       </c>
       <c r="B44" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>136721440</v>
       </c>
       <c r="B45" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>136721450</v>
       </c>
       <c r="B46" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>136721458</v>
       </c>
       <c r="B47" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>136721467</v>
       </c>
       <c r="B48" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>136721800</v>
       </c>
       <c r="B49" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>136721814</v>
       </c>
       <c r="B50" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>136721822</v>
       </c>
       <c r="B51" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>136721847</v>
       </c>
       <c r="B52" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>136721853</v>
       </c>
       <c r="B53" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>136721858</v>
       </c>
       <c r="B54" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>136721902</v>
       </c>
       <c r="B55" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>136782770</v>
       </c>
       <c r="B56" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>136782909</v>
       </c>
       <c r="B57" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>136950604</v>
       </c>
       <c r="B58" t="n">
-        <v>56873</v>
+        <v>56886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>136950780</v>
       </c>
       <c r="B59" t="n">
-        <v>56875</v>
+        <v>56888</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>136950792</v>
       </c>
       <c r="B60" t="n">
-        <v>56875</v>
+        <v>56888</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>136950831</v>
       </c>
       <c r="B61" t="n">
-        <v>56866</v>
+        <v>56879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>136950991</v>
       </c>
       <c r="B62" t="n">
-        <v>56866</v>
+        <v>56879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>136951403</v>
       </c>
       <c r="B63" t="n">
-        <v>56866</v>
+        <v>56879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>136951408</v>
       </c>
       <c r="B64" t="n">
-        <v>56866</v>
+        <v>56879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>136951430</v>
       </c>
       <c r="B65" t="n">
-        <v>56866</v>
+        <v>56879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>136951433</v>
       </c>
       <c r="B66" t="n">
-        <v>56866</v>
+        <v>56879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>136951435</v>
       </c>
       <c r="B67" t="n">
-        <v>56866</v>
+        <v>56879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>136951986</v>
       </c>
       <c r="B68" t="n">
-        <v>56892</v>
+        <v>56905</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>136950615</v>
       </c>
       <c r="B69" t="n">
-        <v>56889</v>
+        <v>56902</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 63185-2025 artfynd.xlsx
+++ b/artfynd/A 63185-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136710326</v>
       </c>
       <c r="B2" t="n">
-        <v>57942</v>
+        <v>57944</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>136710614</v>
       </c>
       <c r="B3" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>136710940</v>
       </c>
       <c r="B4" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>136710989</v>
       </c>
       <c r="B5" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136711032</v>
       </c>
       <c r="B6" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>136711079</v>
       </c>
       <c r="B7" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>136711102</v>
       </c>
       <c r="B8" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136721700</v>
       </c>
       <c r="B9" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136710589</v>
       </c>
       <c r="B10" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>136710395</v>
       </c>
       <c r="B11" t="n">
-        <v>58565</v>
+        <v>58567</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>136710403</v>
       </c>
       <c r="B12" t="n">
-        <v>58565</v>
+        <v>58567</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>136710413</v>
       </c>
       <c r="B13" t="n">
-        <v>58565</v>
+        <v>58567</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>136710423</v>
       </c>
       <c r="B14" t="n">
-        <v>58565</v>
+        <v>58567</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>136710510</v>
       </c>
       <c r="B15" t="n">
-        <v>58565</v>
+        <v>58567</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136710526</v>
       </c>
       <c r="B16" t="n">
-        <v>58565</v>
+        <v>58567</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>136710555</v>
       </c>
       <c r="B17" t="n">
-        <v>58565</v>
+        <v>58567</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>136721693</v>
       </c>
       <c r="B18" t="n">
-        <v>58565</v>
+        <v>58567</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>136679647</v>
       </c>
       <c r="B28" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>136679796</v>
       </c>
       <c r="B29" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>136721202</v>
       </c>
       <c r="B30" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>136721217</v>
       </c>
       <c r="B31" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>136721223</v>
       </c>
       <c r="B32" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>136721231</v>
       </c>
       <c r="B33" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136721238</v>
       </c>
       <c r="B34" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>136721263</v>
       </c>
       <c r="B35" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>136721280</v>
       </c>
       <c r="B36" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>136721286</v>
       </c>
       <c r="B37" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>136721297</v>
       </c>
       <c r="B38" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>136721322</v>
       </c>
       <c r="B39" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>136721334</v>
       </c>
       <c r="B40" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>136721357</v>
       </c>
       <c r="B41" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>136721370</v>
       </c>
       <c r="B42" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>136721387</v>
       </c>
       <c r="B43" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>136721424</v>
       </c>
       <c r="B44" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>136721440</v>
       </c>
       <c r="B45" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>136721450</v>
       </c>
       <c r="B46" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>136721458</v>
       </c>
       <c r="B47" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>136721467</v>
       </c>
       <c r="B48" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>136721800</v>
       </c>
       <c r="B49" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>136721814</v>
       </c>
       <c r="B50" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>136721822</v>
       </c>
       <c r="B51" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>136721847</v>
       </c>
       <c r="B52" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>136721853</v>
       </c>
       <c r="B53" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>136721858</v>
       </c>
       <c r="B54" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>136721902</v>
       </c>
       <c r="B55" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>136782770</v>
       </c>
       <c r="B56" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>136782909</v>
       </c>
       <c r="B57" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>136950604</v>
       </c>
       <c r="B58" t="n">
-        <v>56886</v>
+        <v>56888</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>136950780</v>
       </c>
       <c r="B59" t="n">
-        <v>56888</v>
+        <v>56890</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>136950792</v>
       </c>
       <c r="B60" t="n">
-        <v>56888</v>
+        <v>56890</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>136950831</v>
       </c>
       <c r="B61" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>136950991</v>
       </c>
       <c r="B62" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>136951403</v>
       </c>
       <c r="B63" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>136951408</v>
       </c>
       <c r="B64" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>136951430</v>
       </c>
       <c r="B65" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>136951433</v>
       </c>
       <c r="B66" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>136951435</v>
       </c>
       <c r="B67" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>136951986</v>
       </c>
       <c r="B68" t="n">
-        <v>56905</v>
+        <v>56907</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>136950615</v>
       </c>
       <c r="B69" t="n">
-        <v>56902</v>
+        <v>56904</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 63185-2025 artfynd.xlsx
+++ b/artfynd/A 63185-2025 artfynd.xlsx
@@ -713,17 +713,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -839,11 +831,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -961,17 +949,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1096,11 +1076,7 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1221,11 +1197,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1346,11 +1318,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1471,11 +1439,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1596,11 +1560,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1723,17 +1683,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1856,17 +1808,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1982,11 +1926,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2102,11 +2042,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2212,11 +2148,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2332,11 +2264,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2452,11 +2380,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2572,11 +2496,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2696,11 +2616,7 @@
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -3997,16 +3913,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bofalla, Bofalla, Vrm</t>
@@ -4128,21 +4036,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bofalla, Bofalla, Vrm</t>
@@ -4259,17 +4155,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4390,11 +4278,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4515,11 +4399,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4640,11 +4520,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4765,11 +4641,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4890,11 +4762,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5015,11 +4883,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5140,11 +5004,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5265,11 +5125,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5390,11 +5246,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5515,11 +5367,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5635,11 +5483,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5760,11 +5604,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5885,11 +5725,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6010,11 +5846,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6135,11 +5967,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6260,11 +6088,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6385,11 +6209,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6510,11 +6330,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6635,11 +6451,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6760,11 +6572,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6885,11 +6693,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -7014,11 +6818,7 @@
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -7143,11 +6943,7 @@
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7272,11 +7068,7 @@
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7401,11 +7193,7 @@
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7523,16 +7311,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bofalla, Bofalla, Vrm</t>
@@ -7649,16 +7429,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bofalla, Bofalla, Vrm</t>
@@ -7781,11 +7553,7 @@
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
@@ -7917,11 +7685,7 @@
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>ultraljudsdetektor</t>
@@ -8051,11 +7815,7 @@
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>ultraljudsdetektor</t>
@@ -8181,11 +7941,7 @@
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>ultraljudsdetektor</t>
@@ -8311,11 +8067,7 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>ultraljudsdetektor</t>
@@ -8441,11 +8193,7 @@
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>ultraljudsdetektor</t>
@@ -8571,11 +8319,7 @@
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>ultraljudsdetektor</t>
@@ -8701,11 +8445,7 @@
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>ultraljudsdetektor</t>
@@ -8831,11 +8571,7 @@
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>ultraljudsdetektor</t>
@@ -8961,11 +8697,7 @@
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>ultraljudsdetektor</t>
@@ -9095,11 +8827,7 @@
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>ultraljudsdetektor</t>
@@ -9229,11 +8957,7 @@
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>ultraljudsdetektor</t>

--- a/artfynd/A 63185-2025 artfynd.xlsx
+++ b/artfynd/A 63185-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136710326</v>
       </c>
       <c r="B2" t="n">
-        <v>57944</v>
+        <v>57954</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136710614</v>
       </c>
       <c r="B3" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>136710940</v>
       </c>
       <c r="B4" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>136710989</v>
       </c>
       <c r="B5" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>136711032</v>
       </c>
       <c r="B6" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>136711079</v>
       </c>
       <c r="B7" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>136711102</v>
       </c>
       <c r="B8" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>136721700</v>
       </c>
       <c r="B9" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>136710589</v>
       </c>
       <c r="B10" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>136710395</v>
       </c>
       <c r="B11" t="n">
-        <v>58567</v>
+        <v>58577</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>136710403</v>
       </c>
       <c r="B12" t="n">
-        <v>58567</v>
+        <v>58577</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>136710413</v>
       </c>
       <c r="B13" t="n">
-        <v>58567</v>
+        <v>58577</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136710423</v>
       </c>
       <c r="B14" t="n">
-        <v>58567</v>
+        <v>58577</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>136710510</v>
       </c>
       <c r="B15" t="n">
-        <v>58567</v>
+        <v>58577</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>136710526</v>
       </c>
       <c r="B16" t="n">
-        <v>58567</v>
+        <v>58577</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136710555</v>
       </c>
       <c r="B17" t="n">
-        <v>58567</v>
+        <v>58577</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>136721693</v>
       </c>
       <c r="B18" t="n">
-        <v>58567</v>
+        <v>58577</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>136721202</v>
       </c>
       <c r="B30" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>136721217</v>
       </c>
       <c r="B31" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>136721223</v>
       </c>
       <c r="B32" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>136721231</v>
       </c>
       <c r="B33" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>136721238</v>
       </c>
       <c r="B34" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>136721263</v>
       </c>
       <c r="B35" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>136721280</v>
       </c>
       <c r="B36" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>136721286</v>
       </c>
       <c r="B37" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>136721297</v>
       </c>
       <c r="B38" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>136721322</v>
       </c>
       <c r="B39" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>136721334</v>
       </c>
       <c r="B40" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>136721357</v>
       </c>
       <c r="B41" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>136721370</v>
       </c>
       <c r="B42" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>136721387</v>
       </c>
       <c r="B43" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>136721424</v>
       </c>
       <c r="B44" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>136721440</v>
       </c>
       <c r="B45" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>136721450</v>
       </c>
       <c r="B46" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>136721458</v>
       </c>
       <c r="B47" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>136721467</v>
       </c>
       <c r="B48" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>136721800</v>
       </c>
       <c r="B49" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>136721814</v>
       </c>
       <c r="B50" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>136721822</v>
       </c>
       <c r="B51" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>136721847</v>
       </c>
       <c r="B52" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>136721853</v>
       </c>
       <c r="B53" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>136721858</v>
       </c>
       <c r="B54" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>136721902</v>
       </c>
       <c r="B55" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>136782770</v>
       </c>
       <c r="B56" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>136782909</v>
       </c>
       <c r="B57" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>136950604</v>
       </c>
       <c r="B58" t="n">
-        <v>56888</v>
+        <v>56898</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>136950780</v>
       </c>
       <c r="B59" t="n">
-        <v>56890</v>
+        <v>56900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>136950792</v>
       </c>
       <c r="B60" t="n">
-        <v>56890</v>
+        <v>56900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>136950831</v>
       </c>
       <c r="B61" t="n">
-        <v>56881</v>
+        <v>56891</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>136950991</v>
       </c>
       <c r="B62" t="n">
-        <v>56881</v>
+        <v>56891</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>136951403</v>
       </c>
       <c r="B63" t="n">
-        <v>56881</v>
+        <v>56891</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>136951408</v>
       </c>
       <c r="B64" t="n">
-        <v>56881</v>
+        <v>56891</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136951430</v>
       </c>
       <c r="B65" t="n">
-        <v>56881</v>
+        <v>56891</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>136951433</v>
       </c>
       <c r="B66" t="n">
-        <v>56881</v>
+        <v>56891</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         <v>136951435</v>
       </c>
       <c r="B67" t="n">
-        <v>56881</v>
+        <v>56891</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>136951986</v>
       </c>
       <c r="B68" t="n">
-        <v>56907</v>
+        <v>56917</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>136950615</v>
       </c>
       <c r="B69" t="n">
-        <v>56904</v>
+        <v>56914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 63185-2025 artfynd.xlsx
+++ b/artfynd/A 63185-2025 artfynd.xlsx
@@ -7281,7 +7281,7 @@
         <v>136782770</v>
       </c>
       <c r="B56" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>136782909</v>
       </c>
       <c r="B57" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>136950604</v>
       </c>
       <c r="B58" t="n">
-        <v>56898</v>
+        <v>56899</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>136950780</v>
       </c>
       <c r="B59" t="n">
-        <v>56900</v>
+        <v>56901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>136950792</v>
       </c>
       <c r="B60" t="n">
-        <v>56900</v>
+        <v>56901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>136950831</v>
       </c>
       <c r="B61" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>136950991</v>
       </c>
       <c r="B62" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>136951403</v>
       </c>
       <c r="B63" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>136951408</v>
       </c>
       <c r="B64" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136951430</v>
       </c>
       <c r="B65" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>136951433</v>
       </c>
       <c r="B66" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         <v>136951435</v>
       </c>
       <c r="B67" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>136951986</v>
       </c>
       <c r="B68" t="n">
-        <v>56917</v>
+        <v>56918</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>136950615</v>
       </c>
       <c r="B69" t="n">
-        <v>56914</v>
+        <v>56915</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 63185-2025 artfynd.xlsx
+++ b/artfynd/A 63185-2025 artfynd.xlsx
@@ -7281,7 +7281,7 @@
         <v>136782770</v>
       </c>
       <c r="B56" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>136782909</v>
       </c>
       <c r="B57" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 63185-2025 artfynd.xlsx
+++ b/artfynd/A 63185-2025 artfynd.xlsx
@@ -7522,7 +7522,7 @@
         <v>136950604</v>
       </c>
       <c r="B58" t="n">
-        <v>56899</v>
+        <v>56902</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>136950780</v>
       </c>
       <c r="B59" t="n">
-        <v>56901</v>
+        <v>56904</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>136950792</v>
       </c>
       <c r="B60" t="n">
-        <v>56901</v>
+        <v>56904</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>136950831</v>
       </c>
       <c r="B61" t="n">
-        <v>56892</v>
+        <v>56895</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>136950991</v>
       </c>
       <c r="B62" t="n">
-        <v>56892</v>
+        <v>56895</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>136951403</v>
       </c>
       <c r="B63" t="n">
-        <v>56892</v>
+        <v>56895</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>136951408</v>
       </c>
       <c r="B64" t="n">
-        <v>56892</v>
+        <v>56895</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>136951430</v>
       </c>
       <c r="B65" t="n">
-        <v>56892</v>
+        <v>56895</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>136951433</v>
       </c>
       <c r="B66" t="n">
-        <v>56892</v>
+        <v>56895</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         <v>136951435</v>
       </c>
       <c r="B67" t="n">
-        <v>56892</v>
+        <v>56895</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>136951986</v>
       </c>
       <c r="B68" t="n">
-        <v>56918</v>
+        <v>56921</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>136950615</v>
       </c>
       <c r="B69" t="n">
-        <v>56915</v>
+        <v>56918</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
